--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1018,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118272592</v>
+        <v>118273406</v>
       </c>
       <c r="B5" t="n">
-        <v>8405</v>
+        <v>8416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,13 +1067,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665940</v>
+        <v>665869</v>
       </c>
       <c r="R5" t="n">
-        <v>6570835</v>
+        <v>6570958</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118272468</v>
+        <v>118273685</v>
       </c>
       <c r="B7" t="n">
-        <v>5166</v>
+        <v>4769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,17 +1297,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Masmoberget (Masmoberget), Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665972</v>
+        <v>665771</v>
       </c>
       <c r="R7" t="n">
-        <v>6570787</v>
+        <v>6571011</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118273245</v>
+        <v>118272468</v>
       </c>
       <c r="B8" t="n">
-        <v>5186</v>
+        <v>5166</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665877</v>
+        <v>665972</v>
       </c>
       <c r="R8" t="n">
-        <v>6570941</v>
+        <v>6570787</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118273406</v>
+        <v>118273245</v>
       </c>
       <c r="B9" t="n">
-        <v>8416</v>
+        <v>5186</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665869</v>
+        <v>665877</v>
       </c>
       <c r="R9" t="n">
-        <v>6570958</v>
+        <v>6570941</v>
       </c>
       <c r="S9" t="n">
         <v>40</v>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118273685</v>
+        <v>118272592</v>
       </c>
       <c r="B10" t="n">
-        <v>4769</v>
+        <v>8405</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102306</v>
+        <v>106554</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1663,17 +1663,17 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Masmoberget (Masmoberget), Srm</t>
+          <t>Glömsta (Glömsta), Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665771</v>
+        <v>665940</v>
       </c>
       <c r="R10" t="n">
-        <v>6571011</v>
+        <v>6570835</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1252,10 +1252,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118273685</v>
+        <v>118272468</v>
       </c>
       <c r="B7" t="n">
-        <v>4769</v>
+        <v>5166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1297,17 +1297,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Masmoberget (Masmoberget), Srm</t>
+          <t>Glömsta (Glömsta), Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665771</v>
+        <v>665972</v>
       </c>
       <c r="R7" t="n">
-        <v>6571011</v>
+        <v>6570787</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118272468</v>
+        <v>118273685</v>
       </c>
       <c r="B8" t="n">
-        <v>5166</v>
+        <v>4769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1390,21 +1390,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>102306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1419,17 +1419,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Masmoberget (Masmoberget), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665972</v>
+        <v>665771</v>
       </c>
       <c r="R8" t="n">
-        <v>6570787</v>
+        <v>6571011</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -906,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118275246</v>
+        <v>118273685</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>4769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -918,41 +918,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>102306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gömmaren (Gömmaren), Srm</t>
+          <t>Masmoberget (Masmoberget), Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665825</v>
+        <v>665771</v>
       </c>
       <c r="R4" t="n">
-        <v>6571187</v>
+        <v>6571011</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,6 +1009,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1018,10 +1028,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118273406</v>
+        <v>118272468</v>
       </c>
       <c r="B5" t="n">
-        <v>8416</v>
+        <v>5166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,21 +1044,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1067,13 +1077,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665869</v>
+        <v>665972</v>
       </c>
       <c r="R5" t="n">
-        <v>6570958</v>
+        <v>6570787</v>
       </c>
       <c r="S5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1102,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1112,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118273458</v>
+        <v>118273406</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>8416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,41 +1162,50 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Glömsta (Glömsta), Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665853</v>
+        <v>665869</v>
       </c>
       <c r="R6" t="n">
-        <v>6570996</v>
+        <v>6570958</v>
       </c>
       <c r="S6" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1234,6 +1253,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1252,10 +1272,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118272468</v>
+        <v>118273458</v>
       </c>
       <c r="B7" t="n">
-        <v>5166</v>
+        <v>90524</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,50 +1284,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100526</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Glömsta (Glömsta), Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665972</v>
+        <v>665853</v>
       </c>
       <c r="R7" t="n">
-        <v>6570787</v>
+        <v>6570996</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,7 +1347,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1346,7 +1357,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1366,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1374,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118273685</v>
+        <v>118275246</v>
       </c>
       <c r="B8" t="n">
-        <v>4769</v>
+        <v>90524</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,50 +1396,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102306</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Masmoberget (Masmoberget), Srm</t>
+          <t>Gömmaren (Gömmaren), Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665771</v>
+        <v>665825</v>
       </c>
       <c r="R8" t="n">
-        <v>6571011</v>
+        <v>6571187</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,7 +1478,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118273245</v>
+        <v>118272592</v>
       </c>
       <c r="B9" t="n">
-        <v>5186</v>
+        <v>8405</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1512,21 +1512,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665877</v>
+        <v>665940</v>
       </c>
       <c r="R9" t="n">
-        <v>6570941</v>
+        <v>6570835</v>
       </c>
       <c r="S9" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118272592</v>
+        <v>118273245</v>
       </c>
       <c r="B10" t="n">
-        <v>8405</v>
+        <v>5186</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1634,21 +1634,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106554</v>
+        <v>105930</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665940</v>
+        <v>665877</v>
       </c>
       <c r="R10" t="n">
-        <v>6570835</v>
+        <v>6570941</v>
       </c>
       <c r="S10" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:34</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1738,6 +1738,210 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121409010</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97035</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>665768</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6571477</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121409014</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92008</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>665806</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6570996</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B11" t="n">
-        <v>97035</v>
+        <v>92020</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R11" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B12" t="n">
-        <v>92008</v>
+        <v>97048</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R12" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B11" t="n">
-        <v>92020</v>
+        <v>97049</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R11" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B12" t="n">
-        <v>97048</v>
+        <v>92021</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R12" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B11" t="n">
-        <v>97049</v>
+        <v>92024</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R11" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B12" t="n">
-        <v>92021</v>
+        <v>97052</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R12" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B11" t="n">
-        <v>92024</v>
+        <v>97052</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R11" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B12" t="n">
-        <v>97052</v>
+        <v>92024</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R12" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>121409010</v>
       </c>
       <c r="B11" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>121409014</v>
       </c>
       <c r="B12" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1743,7 +1743,7 @@
         <v>121409010</v>
       </c>
       <c r="B11" t="n">
-        <v>97058</v>
+        <v>97059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>121409014</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>92031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B11" t="n">
-        <v>97059</v>
+        <v>92031</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R11" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B12" t="n">
-        <v>92031</v>
+        <v>97059</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R12" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1740,10 +1740,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409014</v>
+        <v>121409010</v>
       </c>
       <c r="B11" t="n">
-        <v>92031</v>
+        <v>97059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,25 +1752,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665806</v>
+        <v>665768</v>
       </c>
       <c r="R11" t="n">
-        <v>6570996</v>
+        <v>6571477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409010</v>
+        <v>121409014</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>92031</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,25 +1854,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1882,10 +1882,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665768</v>
+        <v>665806</v>
       </c>
       <c r="R12" t="n">
-        <v>6571477</v>
+        <v>6570996</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1942,6 +1942,322 @@
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>131457767</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>665946</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6570767</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>131457546</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79006</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>665841</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6571216</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>131457539</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57884</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>665841</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6571216</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92241</v>
+        <v>92244</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>79010</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92245</v>
+        <v>92251</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79017</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457546</v>
+        <v>131457539</v>
       </c>
       <c r="B14" t="n">
-        <v>79017</v>
+        <v>57895</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,28 +2056,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,18 +2126,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457539</v>
+        <v>131457546</v>
       </c>
       <c r="B15" t="n">
-        <v>57895</v>
+        <v>79017</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,29 +2161,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2236,12 +2230,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457539</v>
       </c>
       <c r="B14" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131457546</v>
       </c>
       <c r="B15" t="n">
-        <v>79017</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92253</v>
+        <v>92256</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457539</v>
+        <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>57896</v>
+        <v>79021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,29 +2056,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2126,12 +2125,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2150,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457546</v>
+        <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,28 +2166,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2230,18 +2236,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457546</v>
+        <v>131457539</v>
       </c>
       <c r="B14" t="n">
-        <v>79021</v>
+        <v>57899</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,28 +2056,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,18 +2126,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457539</v>
+        <v>131457546</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>79021</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,29 +2161,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2236,12 +2230,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457539</v>
+        <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>79021</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,29 +2056,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2126,12 +2125,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2150,10 +2155,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457546</v>
+        <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>79021</v>
+        <v>57899</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,28 +2166,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2230,18 +2236,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92256</v>
+        <v>92262</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457546</v>
       </c>
       <c r="B14" t="n">
-        <v>79021</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         <v>131457539</v>
       </c>
       <c r="B15" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92262</v>
+        <v>92265</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457546</v>
+        <v>131457539</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,28 +2056,29 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2125,18 +2126,12 @@
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2155,10 +2150,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457539</v>
+        <v>131457546</v>
       </c>
       <c r="B15" t="n">
-        <v>57901</v>
+        <v>79026</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,29 +2161,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2236,12 +2230,18 @@
           <t>2026-03-05</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -1947,7 +1947,7 @@
         <v>131457767</v>
       </c>
       <c r="B13" t="n">
-        <v>92265</v>
+        <v>92270</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2048,7 +2048,7 @@
         <v>131457539</v>
       </c>
       <c r="B14" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2153,7 +2153,7 @@
         <v>131457546</v>
       </c>
       <c r="B15" t="n">
-        <v>79026</v>
+        <v>79031</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113384206</v>
+        <v>131457522</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Masmo, Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>665948</v>
+        <v>665845</v>
       </c>
       <c r="R2" t="n">
-        <v>6570769</v>
+        <v>6571188</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113388221</v>
+        <v>131457739</v>
       </c>
       <c r="B3" t="n">
-        <v>90352</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,38 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Masmo, Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>665743</v>
+        <v>665864</v>
       </c>
       <c r="R3" t="n">
-        <v>6571171</v>
+        <v>6570913</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -864,22 +844,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:31</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,80 +858,73 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Johansson</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118273685</v>
+        <v>113384206</v>
       </c>
       <c r="B4" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Masmoberget (Masmoberget), Srm</t>
+          <t>Masmo, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>665771</v>
+        <v>665948</v>
       </c>
       <c r="R4" t="n">
-        <v>6571011</v>
+        <v>6570769</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,22 +948,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,81 +972,69 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118272468</v>
+        <v>131457776</v>
       </c>
       <c r="B5" t="n">
-        <v>5166</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>665972</v>
+        <v>665967</v>
       </c>
       <c r="R5" t="n">
-        <v>6570787</v>
+        <v>6570752</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1107,22 +1058,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:54</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,27 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118273406</v>
+        <v>131457802</v>
       </c>
       <c r="B6" t="n">
-        <v>8416</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,46 +1102,40 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>665869</v>
+        <v>666003</v>
       </c>
       <c r="R6" t="n">
-        <v>6570958</v>
+        <v>6570761</v>
       </c>
       <c r="S6" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,22 +1159,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>11:45</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,65 +1180,68 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118273458</v>
+        <v>117906821</v>
       </c>
       <c r="B7" t="n">
-        <v>90524</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Gömmaren / Glömsta, Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>665853</v>
+        <v>665826</v>
       </c>
       <c r="R7" t="n">
-        <v>6570996</v>
+        <v>6571161</v>
       </c>
       <c r="S7" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,22 +1265,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:50</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1366,71 +1279,70 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nina Tadsen</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118275246</v>
+        <v>131457767</v>
       </c>
       <c r="B8" t="n">
-        <v>90524</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gömmaren (Gömmaren), Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>665825</v>
+        <v>665946</v>
       </c>
       <c r="R8" t="n">
-        <v>6571187</v>
+        <v>6570767</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1454,22 +1366,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:37</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,77 +1380,65 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118272592</v>
+        <v>113388221</v>
       </c>
       <c r="B9" t="n">
-        <v>8405</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106554</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Masmo, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>665940</v>
+        <v>665743</v>
       </c>
       <c r="R9" t="n">
-        <v>6570835</v>
+        <v>6571171</v>
       </c>
       <c r="S9" t="n">
         <v>30</v>
@@ -1575,22 +1465,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2023-11-24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,81 +1489,66 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jakob Nygren</t>
+          <t>Nicklas Johansson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118273245</v>
+        <v>118273458</v>
       </c>
       <c r="B10" t="n">
-        <v>5186</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>105930</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Glömsta (Glömsta), Srm</t>
+          <t>Glömsta, Glömsta, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>665877</v>
+        <v>665853</v>
       </c>
       <c r="R10" t="n">
-        <v>6570941</v>
+        <v>6570996</v>
       </c>
       <c r="S10" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1702,7 +1577,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1712,7 +1587,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:34</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1721,7 +1596,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1740,53 +1614,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121409010</v>
+        <v>118275246</v>
       </c>
       <c r="B11" t="n">
-        <v>97067</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gömmaren, Srm</t>
+          <t>Gömmaren, Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>665768</v>
+        <v>665825</v>
       </c>
       <c r="R11" t="n">
-        <v>6571477</v>
+        <v>6571187</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1810,12 +1679,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,27 +1709,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jakob Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121409014</v>
+        <v>131457714</v>
       </c>
       <c r="B12" t="n">
-        <v>92039</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1858,34 +1732,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gömmaren, Srm</t>
+          <t>Gömmarens naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>665806</v>
+        <v>665828</v>
       </c>
       <c r="R12" t="n">
-        <v>6570996</v>
+        <v>6571120</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,12 +1789,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,66 +1803,64 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>August Oljeqvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131457767</v>
+        <v>121409014</v>
       </c>
       <c r="B13" t="n">
-        <v>92270</v>
+        <v>93235</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4217</v>
+        <v>5966</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Gömmarens naturreservat, Srm</t>
+          <t>Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>665946</v>
+        <v>665806</v>
       </c>
       <c r="R13" t="n">
-        <v>6570767</v>
+        <v>6570996</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,12 +1887,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2026,29 +1901,28 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131457539</v>
+        <v>121409015</v>
       </c>
       <c r="B14" t="n">
-        <v>57909</v>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,42 +1930,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Gömmarens naturreservat, Srm</t>
+          <t>Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>665841</v>
+        <v>665910</v>
       </c>
       <c r="R14" t="n">
-        <v>6571216</v>
+        <v>6570979</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,12 +1984,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2138,22 +2004,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>August Oljeqvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131457546</v>
+        <v>121409019</v>
       </c>
       <c r="B15" t="n">
-        <v>79031</v>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2161,41 +2027,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Gömmarens naturreservat, Srm</t>
+          <t>Gömmaren, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>665841</v>
+        <v>665732</v>
       </c>
       <c r="R15" t="n">
-        <v>6571216</v>
+        <v>6571440</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2222,17 +2081,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På tallbark.</t>
+          <t>2024-11-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2241,22 +2095,1547 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>131457519</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>665845</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6571188</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
           <t>August Oljeqvist</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
+      <c r="AX16" t="inlineStr">
         <is>
           <t>August Oljeqvist</t>
         </is>
       </c>
-      <c r="AY15" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>131457546</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>665841</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6571216</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>131457715</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>665828</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6571120</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>131456706</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>666081</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6570892</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På tallbark.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>131457711</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>665828</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6571120</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>131457725</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>665879</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6571019</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131457539</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>665841</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6571216</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131457826</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Gömmarens naturreservat, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>666003</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6570761</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118272468</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Glömsta, Glömsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>665972</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6570787</v>
+      </c>
+      <c r="S24" t="n">
+        <v>30</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118273685</v>
+      </c>
+      <c r="B25" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Masmoberget, Masmoberget, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>665771</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6571011</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118273245</v>
+      </c>
+      <c r="B26" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Glömsta, Glömsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>665877</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6570941</v>
+      </c>
+      <c r="S26" t="n">
+        <v>40</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118273406</v>
+      </c>
+      <c r="B27" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Glömsta, Glömsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>665869</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6570958</v>
+      </c>
+      <c r="S27" t="n">
+        <v>40</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118272592</v>
+      </c>
+      <c r="B28" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Glömsta, Glömsta, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>665940</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6570835</v>
+      </c>
+      <c r="S28" t="n">
+        <v>30</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jakob Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121409010</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gömmaren, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>665768</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6571477</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-11-03</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24264-2023 artfynd.xlsx
+++ b/artfynd/A 24264-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457739</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113384206</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457776</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457802</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906821</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457767</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113388221</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1611,6 +1656,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273458</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1718,6 +1768,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118275246</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1819,6 +1874,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457714</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1916,6 +1976,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121409014</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2013,6 +2078,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121409015</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121409019</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2220,6 +2295,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457519</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2330,6 +2410,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457546</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2436,6 +2521,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457715</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2542,6 +2632,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131456706</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2643,6 +2738,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457711</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2744,6 +2844,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457725</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2849,6 +2954,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457539</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2954,6 +3064,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131457826</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3071,6 +3186,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272468</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3188,6 +3308,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273685</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3305,6 +3430,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273245</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3422,6 +3552,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273406</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3539,6 +3674,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118272592</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3636,8 +3776,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121409010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>